--- a/result/ECT2_LUAD_Tables.xlsx
+++ b/result/ECT2_LUAD_Tables.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 3.1 (Cox)_stage_continuous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1677,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1693,6 +1694,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>P-value</t>
         </is>
       </c>
@@ -1706,7 +1717,13 @@
       <c r="B2" t="n">
         <v>1.013</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>0.170</t>
         </is>
@@ -1721,7 +1738,13 @@
       <c r="B3" t="n">
         <v>1.001</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>0.859</t>
         </is>
@@ -1736,7 +1759,13 @@
       <c r="B4" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>0.004</t>
         </is>
@@ -1751,7 +1780,13 @@
       <c r="B5" t="n">
         <v>1.233</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.814</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>0.288</t>
         </is>
@@ -1766,7 +1801,13 @@
       <c r="B6" t="n">
         <v>1.874</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.989</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>0.008</t>
         </is>
@@ -1781,7 +1822,13 @@
       <c r="B7" t="n">
         <v>2.688</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="n">
+        <v>1.676</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.311</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -1796,7 +1843,13 @@
       <c r="B8" t="n">
         <v>2.696</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.453</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>0.006</t>
         </is>
@@ -1813,18 +1866,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Clinical Variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Coefficient</t>
+          <t>Hazard Ratio (HR)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1844,902 +1897,109 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <f>== [ Model: Pathologic Stage ] ===</f>
-        <v/>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.121</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ECT2expression</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.910</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ECT2expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_stage)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.0378</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>ECT2group_Low</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>5.1463e-02</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1371.585</v>
-      </c>
-      <c r="C8" t="n">
-        <v>715.6464</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2027.5236</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>145.9375</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-53.8058</v>
-      </c>
-      <c r="D9" t="n">
-        <v>345.6808</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>179.3667</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-60.6498</v>
-      </c>
-      <c r="D10" t="n">
-        <v>419.3832</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.142</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>270.4498</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.9336</v>
-      </c>
-      <c r="D11" t="n">
-        <v>537.966</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.048</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>255.3675</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-190.6057</v>
-      </c>
-      <c r="D12" t="n">
-        <v>701.3407</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.261</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-7.2617</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-16.9531</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.4296</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.141</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.2805</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.3355</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5.8965</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.216</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <f>== [ Model: Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ECT2expression</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ECT2expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_T)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.0395</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3.9720e-02</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1323.2218</v>
-      </c>
-      <c r="C22" t="n">
-        <v>667.5852</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1978.8584</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>115.5155</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-85.4884</v>
-      </c>
-      <c r="D23" t="n">
-        <v>316.5195</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.259</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>277.4272</v>
-      </c>
-      <c r="C24" t="n">
-        <v>63.0546</v>
-      </c>
-      <c r="D24" t="n">
-        <v>491.7998</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.011</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>139.1544</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-222.4181</v>
-      </c>
-      <c r="D25" t="n">
-        <v>500.7269</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.450</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>79.12439999999999</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-431.9856</v>
-      </c>
-      <c r="D26" t="n">
-        <v>590.2344000000001</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0.761</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>-7.1271</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-16.6929</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2.4388</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.144</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2.1962</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-1.4047</v>
-      </c>
-      <c r="D28" t="n">
-        <v>5.7972</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.231</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <f>== [ Model: Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ECT2expression</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ECT2expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_N)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>0.0358</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>6.7354e-02</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1411.7709</v>
-      </c>
-      <c r="C36" t="n">
-        <v>754.583</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2068.9588</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>130.2491</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-70.3009</v>
-      </c>
-      <c r="D37" t="n">
-        <v>330.7992</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.202</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>169.0698</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-84.1412</v>
-      </c>
-      <c r="D38" t="n">
-        <v>422.2809</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.190</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>294.5591</v>
-      </c>
-      <c r="C39" t="n">
-        <v>11.2557</v>
-      </c>
-      <c r="D39" t="n">
-        <v>577.8625</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>-544.5187</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-1794.9663</v>
-      </c>
-      <c r="D40" t="n">
-        <v>705.9289</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.392</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>-7.2486</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-17.0324</v>
-      </c>
-      <c r="D41" t="n">
-        <v>2.5353</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.146</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2.3555</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.2882</v>
-      </c>
-      <c r="D42" t="n">
-        <v>5.9992</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.204</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <f>== [ Model: Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ECT2expression</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ECT2expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_M)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0261</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1.8866e-01</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1977.0056</v>
-      </c>
-      <c r="C50" t="n">
-        <v>1212.3729</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2741.6384</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>70.7069</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-166.3438</v>
-      </c>
-      <c r="D51" t="n">
-        <v>307.7577</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.557</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C(pathologic_M)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>98.3267</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-351.9584</v>
-      </c>
-      <c r="D52" t="n">
-        <v>548.6118</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>-13.1899</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-24.7087</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-1.671</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.025</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1.3639</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-2.9995</v>
-      </c>
-      <c r="D54" t="n">
-        <v>5.7273</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.539</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.811</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.260</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2752,6 +2012,1117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ECT2expression</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ECT2expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.0199</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8.4703e-02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1504.9426</v>
+      </c>
+      <c r="C8" t="n">
+        <v>865.6339</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2144.2513</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>170.5751</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-25.943</v>
+      </c>
+      <c r="D9" t="n">
+        <v>367.0932</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.089</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-7.5628</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-17.1548</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.0291</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.122</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.7923</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.8068</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.3914</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.328</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ECT2expression</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ECT2expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0378</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5.1463e-02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1371.585</v>
+      </c>
+      <c r="C19" t="n">
+        <v>715.6464</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2027.5236</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>145.9375</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-53.8058</v>
+      </c>
+      <c r="D20" t="n">
+        <v>345.6808</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>179.3667</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-60.6498</v>
+      </c>
+      <c r="D21" t="n">
+        <v>419.3832</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.142</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>270.4498</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.9336</v>
+      </c>
+      <c r="D22" t="n">
+        <v>537.966</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.048</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>255.3675</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-190.6057</v>
+      </c>
+      <c r="D23" t="n">
+        <v>701.3407</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.261</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-7.2617</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-16.9531</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.4296</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.141</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2.2805</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.3355</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5.8965</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.216</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ECT2expression</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ECT2expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.0395</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3.9720e-02</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1323.2218</v>
+      </c>
+      <c r="C33" t="n">
+        <v>667.5852</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1978.8584</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>115.5155</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-85.4884</v>
+      </c>
+      <c r="D34" t="n">
+        <v>316.5195</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.259</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>277.4272</v>
+      </c>
+      <c r="C35" t="n">
+        <v>63.0546</v>
+      </c>
+      <c r="D35" t="n">
+        <v>491.7998</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>139.1544</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-222.4181</v>
+      </c>
+      <c r="D36" t="n">
+        <v>500.7269</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.450</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>79.12439999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-431.9856</v>
+      </c>
+      <c r="D37" t="n">
+        <v>590.2344000000001</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.761</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-7.1271</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-16.6929</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.4388</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2.1962</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.4047</v>
+      </c>
+      <c r="D39" t="n">
+        <v>5.7972</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.231</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ECT2expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ECT2expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0358</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>6.7354e-02</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1411.7709</v>
+      </c>
+      <c r="C47" t="n">
+        <v>754.583</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2068.9588</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>130.2491</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-70.3009</v>
+      </c>
+      <c r="D48" t="n">
+        <v>330.7992</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.202</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>169.0698</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-84.1412</v>
+      </c>
+      <c r="D49" t="n">
+        <v>422.2809</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.190</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>294.5591</v>
+      </c>
+      <c r="C50" t="n">
+        <v>11.2557</v>
+      </c>
+      <c r="D50" t="n">
+        <v>577.8625</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.042</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>-544.5187</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-1794.9663</v>
+      </c>
+      <c r="D51" t="n">
+        <v>705.9289</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.392</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>-7.2486</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-17.0324</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.5353</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.146</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2.3555</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-1.2882</v>
+      </c>
+      <c r="D53" t="n">
+        <v>5.9992</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.204</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ECT2expression</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ECT2expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0261</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1.8866e-01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1977.0056</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1212.3729</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2741.6384</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>70.7069</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-166.3438</v>
+      </c>
+      <c r="D62" t="n">
+        <v>307.7577</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0.557</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>98.3267</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-351.9584</v>
+      </c>
+      <c r="D63" t="n">
+        <v>548.6118</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>-13.1899</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-24.7087</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-1.671</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0.025</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1.3639</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-2.9995</v>
+      </c>
+      <c r="D65" t="n">
+        <v>5.7273</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0.539</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/result/ECT2_LUAD_Tables.xlsx
+++ b/result/ECT2_LUAD_Tables.xlsx
@@ -875,27 +875,27 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>EGFRExpression</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>KrasExpression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ALKExpression</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>BRAFExpression</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
     </row>
@@ -927,27 +927,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0.010</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>0.219</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>-0.026</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>-0.014</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.150</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-0.099</t>
         </is>
       </c>
     </row>
@@ -971,27 +971,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0.831</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.563</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>0.765</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.151</t>
         </is>
       </c>
     </row>
@@ -1023,27 +1023,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>-0.039</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.046</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>-0.016</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -1067,27 +1067,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.837</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>0.482</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.408</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.859</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0.774</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.611</t>
         </is>
       </c>
     </row>
@@ -1119,27 +1119,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>-0.001</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>-0.022</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.072</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>-0.048</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>-0.050</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1163,34 +1163,34 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0.983</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>0.624</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0.112</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>0.291</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.265</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.865</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>EGFRExpression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1220,22 +1220,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.057</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.061</t>
         </is>
       </c>
     </row>
@@ -1248,45 +1248,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.831</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>0.837</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>0.983</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.595</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.177</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>KrasExpression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,42 +1296,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-0.039</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>-0.057</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.067</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.080</t>
         </is>
       </c>
     </row>
@@ -1344,45 +1344,45 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.482</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.624</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.078</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1392,42 +1392,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.014</t>
+          <t>-0.026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.048</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.067</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.040</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.003</t>
         </is>
       </c>
     </row>
@@ -1440,45 +1440,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>0.563</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.940</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRAFExpression</t>
+          <t>ALKExpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.150</t>
+          <t>-0.014</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.067</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>-0.040</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.107</t>
         </is>
       </c>
     </row>
@@ -1536,45 +1536,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.595</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.372</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EGFR_Mut_Binary</t>
+          <t>BRAFExpression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1584,37 +1584,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.099</t>
+          <t>0.150</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1632,37 +1632,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.774</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.940</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1678,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,15 +1694,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1717,13 +1712,12 @@
       <c r="B2" t="n">
         <v>1.013</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.994</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.033</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.994-1.033</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.170</t>
         </is>
@@ -1738,13 +1732,12 @@
       <c r="B3" t="n">
         <v>1.001</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.993</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.993-1.008</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.859</t>
         </is>
@@ -1759,13 +1752,12 @@
       <c r="B4" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.381-0.830</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.004</t>
         </is>
@@ -1780,13 +1772,12 @@
       <c r="B5" t="n">
         <v>1.233</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.814</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.838-1.814</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.288</t>
         </is>
@@ -1801,13 +1792,12 @@
       <c r="B6" t="n">
         <v>1.874</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.175</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2.989</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.175-2.989</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.008</t>
         </is>
@@ -1822,13 +1812,12 @@
       <c r="B7" t="n">
         <v>2.688</v>
       </c>
-      <c r="C7" t="n">
-        <v>1.676</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.311</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.676-4.311</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -1843,13 +1832,12 @@
       <c r="B8" t="n">
         <v>2.696</v>
       </c>
-      <c r="C8" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5.453</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.333-5.453</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>0.006</t>
         </is>
@@ -1866,7 +1854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1882,15 +1870,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1905,13 +1888,12 @@
       <c r="B2" t="n">
         <v>1.015</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.034</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.996-1.034</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.121</t>
         </is>
@@ -1926,13 +1908,12 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.993</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.993-1.008</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.910</t>
         </is>
@@ -1947,13 +1928,12 @@
       <c r="B4" t="n">
         <v>1.492</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.781</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.250-1.781</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -1968,13 +1948,12 @@
       <c r="B5" t="n">
         <v>0.537</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.788</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.366-0.788</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.001</t>
         </is>
@@ -1989,13 +1968,12 @@
       <c r="B6" t="n">
         <v>1.242</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.852-1.811</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.260</t>
         </is>
@@ -2012,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2028,15 +2006,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -2050,7 +2023,6 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2065,7 +2037,6 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2080,7 +2051,6 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2095,7 +2065,6 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2110,7 +2079,6 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2121,7 +2089,6 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2130,15 +2097,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1504.9426</v>
-      </c>
-      <c r="C8" t="n">
-        <v>865.6339</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2144.2513</v>
-      </c>
-      <c r="E8" t="inlineStr">
+        <v>1504.943</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>865.634-2144.251</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2151,15 +2117,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>170.5751</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-25.943</v>
-      </c>
-      <c r="D9" t="n">
-        <v>367.0932</v>
-      </c>
-      <c r="E9" t="inlineStr">
+        <v>170.575</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-25.943-367.093</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>0.089</t>
         </is>
@@ -2172,15 +2137,14 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-7.5628</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-17.1548</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.0291</v>
-      </c>
-      <c r="E10" t="inlineStr">
+        <v>-7.563</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-17.155-2.029</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>0.122</t>
         </is>
@@ -2193,15 +2157,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7923</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.8068</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5.3914</v>
-      </c>
-      <c r="E11" t="inlineStr">
+        <v>1.792</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-1.807-5.391</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>0.328</t>
         </is>
@@ -2212,7 +2175,6 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13">
@@ -2222,7 +2184,6 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2237,7 +2198,6 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2252,7 +2212,6 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2267,7 +2226,6 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2282,7 +2240,6 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2293,7 +2250,6 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2304,13 +2260,12 @@
       <c r="B19" t="n">
         <v>1371.585</v>
       </c>
-      <c r="C19" t="n">
-        <v>715.6464</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2027.5236</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>715.646-2027.524</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2323,15 +2278,14 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>145.9375</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-53.8058</v>
-      </c>
-      <c r="D20" t="n">
-        <v>345.6808</v>
-      </c>
-      <c r="E20" t="inlineStr">
+        <v>145.938</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-53.806-345.681</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>0.152</t>
         </is>
@@ -2344,15 +2298,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>179.3667</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-60.6498</v>
-      </c>
-      <c r="D21" t="n">
-        <v>419.3832</v>
-      </c>
-      <c r="E21" t="inlineStr">
+        <v>179.367</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-60.65-419.383</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>0.142</t>
         </is>
@@ -2365,15 +2318,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>270.4498</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.9336</v>
-      </c>
-      <c r="D22" t="n">
-        <v>537.966</v>
-      </c>
-      <c r="E22" t="inlineStr">
+        <v>270.45</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2.934-537.966</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>0.048</t>
         </is>
@@ -2386,15 +2338,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>255.3675</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-190.6057</v>
-      </c>
-      <c r="D23" t="n">
-        <v>701.3407</v>
-      </c>
-      <c r="E23" t="inlineStr">
+        <v>255.367</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-190.606-701.341</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>0.261</t>
         </is>
@@ -2407,15 +2358,14 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-7.2617</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-16.9531</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.4296</v>
-      </c>
-      <c r="E24" t="inlineStr">
+        <v>-7.262</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-16.953-2.43</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>0.141</t>
         </is>
@@ -2428,15 +2378,14 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.2805</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-1.3355</v>
-      </c>
-      <c r="D25" t="n">
-        <v>5.8965</v>
-      </c>
-      <c r="E25" t="inlineStr">
+        <v>2.281</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-1.336-5.897</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>0.216</t>
         </is>
@@ -2447,7 +2396,6 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27">
@@ -2457,7 +2405,6 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2472,7 +2419,6 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2487,7 +2433,6 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2502,7 +2447,6 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2517,7 +2461,6 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2528,7 +2471,6 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2537,15 +2479,14 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1323.2218</v>
-      </c>
-      <c r="C33" t="n">
-        <v>667.5852</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1978.8584</v>
-      </c>
-      <c r="E33" t="inlineStr">
+        <v>1323.222</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>667.585-1978.858</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2558,15 +2499,14 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>115.5155</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-85.4884</v>
-      </c>
-      <c r="D34" t="n">
-        <v>316.5195</v>
-      </c>
-      <c r="E34" t="inlineStr">
+        <v>115.516</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-85.488-316.519</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>0.259</t>
         </is>
@@ -2579,15 +2519,14 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>277.4272</v>
-      </c>
-      <c r="C35" t="n">
-        <v>63.0546</v>
-      </c>
-      <c r="D35" t="n">
-        <v>491.7998</v>
-      </c>
-      <c r="E35" t="inlineStr">
+        <v>277.427</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>63.055-491.8</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>0.011</t>
         </is>
@@ -2600,15 +2539,14 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>139.1544</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-222.4181</v>
-      </c>
-      <c r="D36" t="n">
-        <v>500.7269</v>
-      </c>
-      <c r="E36" t="inlineStr">
+        <v>139.154</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-222.418-500.727</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>0.450</t>
         </is>
@@ -2621,15 +2559,14 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>79.12439999999999</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-431.9856</v>
-      </c>
-      <c r="D37" t="n">
-        <v>590.2344000000001</v>
-      </c>
-      <c r="E37" t="inlineStr">
+        <v>79.124</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-431.986-590.234</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>0.761</t>
         </is>
@@ -2642,15 +2579,14 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-7.1271</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-16.6929</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2.4388</v>
-      </c>
-      <c r="E38" t="inlineStr">
+        <v>-7.127</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-16.693-2.439</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>0.144</t>
         </is>
@@ -2663,15 +2599,14 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.1962</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-1.4047</v>
-      </c>
-      <c r="D39" t="n">
-        <v>5.7972</v>
-      </c>
-      <c r="E39" t="inlineStr">
+        <v>2.196</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>-1.405-5.797</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>0.231</t>
         </is>
@@ -2682,7 +2617,6 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41">
@@ -2692,7 +2626,6 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2707,7 +2640,6 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2722,7 +2654,6 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2737,7 +2668,6 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2752,7 +2682,6 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2763,7 +2692,6 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2772,15 +2700,14 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1411.7709</v>
-      </c>
-      <c r="C47" t="n">
-        <v>754.583</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2068.9588</v>
-      </c>
-      <c r="E47" t="inlineStr">
+        <v>1411.771</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>754.583-2068.959</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -2793,15 +2720,14 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>130.2491</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-70.3009</v>
-      </c>
-      <c r="D48" t="n">
-        <v>330.7992</v>
-      </c>
-      <c r="E48" t="inlineStr">
+        <v>130.249</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>-70.301-330.799</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>0.202</t>
         </is>
@@ -2814,15 +2740,14 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>169.0698</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-84.1412</v>
-      </c>
-      <c r="D49" t="n">
-        <v>422.2809</v>
-      </c>
-      <c r="E49" t="inlineStr">
+        <v>169.07</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-84.141-422.281</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>0.190</t>
         </is>
@@ -2835,15 +2760,14 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>294.5591</v>
-      </c>
-      <c r="C50" t="n">
-        <v>11.2557</v>
-      </c>
-      <c r="D50" t="n">
-        <v>577.8625</v>
-      </c>
-      <c r="E50" t="inlineStr">
+        <v>294.559</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>11.256-577.863</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>0.042</t>
         </is>
@@ -2856,15 +2780,14 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-544.5187</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-1794.9663</v>
-      </c>
-      <c r="D51" t="n">
-        <v>705.9289</v>
-      </c>
-      <c r="E51" t="inlineStr">
+        <v>-544.519</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-1794.966-705.929</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>0.392</t>
         </is>
@@ -2877,15 +2800,14 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-7.2486</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-17.0324</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2.5353</v>
-      </c>
-      <c r="E52" t="inlineStr">
+        <v>-7.249</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-17.032-2.535</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>0.146</t>
         </is>
@@ -2898,15 +2820,14 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.3555</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-1.2882</v>
-      </c>
-      <c r="D53" t="n">
-        <v>5.9992</v>
-      </c>
-      <c r="E53" t="inlineStr">
+        <v>2.355</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>-1.288-5.999</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>0.204</t>
         </is>
@@ -2917,7 +2838,6 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55">
@@ -2927,7 +2847,6 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2942,7 +2861,6 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2957,7 +2875,6 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2972,7 +2889,6 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2987,7 +2903,6 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2998,7 +2913,6 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3007,15 +2921,14 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1977.0056</v>
-      </c>
-      <c r="C61" t="n">
-        <v>1212.3729</v>
-      </c>
-      <c r="D61" t="n">
-        <v>2741.6384</v>
-      </c>
-      <c r="E61" t="inlineStr">
+        <v>1977.006</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1212.373-2741.638</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -3028,15 +2941,14 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>70.7069</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-166.3438</v>
-      </c>
-      <c r="D62" t="n">
-        <v>307.7577</v>
-      </c>
-      <c r="E62" t="inlineStr">
+        <v>70.70699999999999</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-166.344-307.758</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>0.557</t>
         </is>
@@ -3049,15 +2961,14 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>98.3267</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-351.9584</v>
-      </c>
-      <c r="D63" t="n">
-        <v>548.6118</v>
-      </c>
-      <c r="E63" t="inlineStr">
+        <v>98.327</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-351.958-548.612</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>0.667</t>
         </is>
@@ -3070,15 +2981,14 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-13.1899</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-24.7087</v>
-      </c>
-      <c r="D64" t="n">
-        <v>-1.671</v>
-      </c>
-      <c r="E64" t="inlineStr">
+        <v>-13.19</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-24.709--1.671</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>0.025</t>
         </is>
@@ -3091,15 +3001,14 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1.3639</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-2.9995</v>
-      </c>
-      <c r="D65" t="n">
-        <v>5.7273</v>
-      </c>
-      <c r="E65" t="inlineStr">
+        <v>1.364</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-2.999-5.727</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>0.539</t>
         </is>
@@ -3110,7 +3019,6 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
